--- a/data/trans_bre/P2A_psíq_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_psíq_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,44</t>
+          <t>-1,2; 0,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 2,36</t>
+          <t>-1,45; 2,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,31</t>
+          <t>-0,91; 1,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,54</t>
+          <t>0,1; 2,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 241,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,91; 157,31</t>
+          <t>-41,16; 136,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-62,06; 249,63</t>
+          <t>-65,3; 254,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 422,25</t>
+          <t>-1,83; 398,81</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,03</t>
+          <t>-1,11; 1,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,43</t>
+          <t>-0,87; 1,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,49</t>
+          <t>-0,72; 1,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 2,45</t>
+          <t>0,15; 2,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,59; 170,4</t>
+          <t>-63,35; 126,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,05; 138,72</t>
+          <t>-44,49; 146,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,26; 204,9</t>
+          <t>-47,14; 189,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,26; 289,86</t>
+          <t>4,83; 293,4</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,73</t>
+          <t>0,13; 2,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,04</t>
+          <t>-1,05; 1,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,52</t>
+          <t>-0,41; 1,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 53,62</t>
+          <t>-0,86; 58,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,22; 1455,87</t>
+          <t>-19,18; 1379,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-69,91; 206,4</t>
+          <t>-70,44; 180,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-60,67; 771,54</t>
+          <t>-60,93; 624,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,94; 2729,31</t>
+          <t>-25,18; 3058,69</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,08</t>
+          <t>-0,71; 1,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,66</t>
+          <t>-1,45; 1,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,63</t>
+          <t>0,4; 2,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,67</t>
+          <t>-1,65; 1,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,1; 224,28</t>
+          <t>-50,68; 211,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,66; 108,59</t>
+          <t>-48,53; 99,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,88; 543,56</t>
+          <t>22,83; 561,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,96; 84,68</t>
+          <t>-41,1; 70,8</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,77</t>
+          <t>-0,26; 0,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,94</t>
+          <t>-0,47; 0,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,21</t>
+          <t>0,09; 1,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 23,22</t>
+          <t>0,4; 23,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 109,91</t>
+          <t>-23,31; 118,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 64,93</t>
+          <t>-21,19; 57,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,55; 179,03</t>
+          <t>7,09; 167,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,85; 1267,66</t>
+          <t>18,79; 1251,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_psíq_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_psíq_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>110,62%</t>
+          <t>142,15%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,45</t>
+          <t>-1,12; 0,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,3</t>
+          <t>-1,37; 2,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,33</t>
+          <t>-1,03; 1,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,52</t>
+          <t>0,23; 2,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 241,47</t>
+          <t>-100,0; 254,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,16; 136,05</t>
+          <t>-39,8; 148,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-65,3; 254,58</t>
+          <t>-65,74; 236,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 398,81</t>
+          <t>7,09; 431,96</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>45,66%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,0</t>
+          <t>-1,12; 0,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,45</t>
+          <t>-0,94; 1,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,51</t>
+          <t>-0,68; 1,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,42</t>
+          <t>-0,39; 2,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,35; 126,86</t>
+          <t>-63,36; 120,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,49; 146,67</t>
+          <t>-46,25; 131,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,14; 189,75</t>
+          <t>-41,71; 196,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 293,4</t>
+          <t>-16,18; 144,52</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21,26</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>691,98%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,65</t>
+          <t>-0,06; 2,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,05</t>
+          <t>-1,28; 1,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,58</t>
+          <t>-0,42; 1,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 58,25</t>
+          <t>-1,41; 2,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 1379,65</t>
+          <t>-33,58; 1326,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-70,44; 180,66</t>
+          <t>-70,14; 223,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-60,93; 624,5</t>
+          <t>-46,48; 786,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,18; 3058,69</t>
+          <t>-35,6; 109,05</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,13</t>
+          <t>-0,81; 1,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,48</t>
+          <t>-1,23; 1,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,77</t>
+          <t>0,46; 2,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,53</t>
+          <t>-1,45; 1,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,68; 211,76</t>
+          <t>-57,53; 219,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,53; 99,6</t>
+          <t>-43,54; 99,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,83; 561,31</t>
+          <t>28,6; 589,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,1; 70,8</t>
+          <t>-35,26; 87,16</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,09</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>288,49%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,76</t>
+          <t>-0,26; 0,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,88</t>
+          <t>-0,46; 0,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,2</t>
+          <t>0,11; 1,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 23,21</t>
+          <t>0,03; 1,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 118,21</t>
+          <t>-26,02; 112,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 57,91</t>
+          <t>-21,21; 64,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,09; 167,0</t>
+          <t>4,71; 172,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,79; 1251,88</t>
+          <t>0,47; 80,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_psíq_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_psíq_R-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
